--- a/data/trans_orig/P25D_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P25D_R-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma diariamente tabaco no tradicional  (se incluyen pipas de agua, cachimbas, vapeadores, cigarrillos electrónicos) en 2023</t>
+          <t>Población que fuma diariamente tabaco no tradicional  (se incluyen pipas de agua, cachimbas, vapeadores, cigarrillos electrónicos) en 2023 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3229</t>
+          <t>2876</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27103</t>
+          <t>27584</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,82 +745,82 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>0,72%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>6,9%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>4020</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>13279</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>4,24%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>14478</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>5743</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>32241</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>2,03%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>0,81%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,78%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>4020</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>14048</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>4,49%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>14478</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>5498</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>32485</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>2,03%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>372884</t>
+          <t>372403</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>396758</t>
+          <t>397111</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,82 +858,82 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>99,28%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>309180</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>299921</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>313200</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>98,72%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>95,76%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>698709</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>680946</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>707444</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>97,97%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>95,48%</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
           <t>99,19%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>309180</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>299152</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>313200</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,72%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>95,51%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>698709</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>680702</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>707689</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>97,97%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>95,45%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>99,23%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1602</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13901</t>
+          <t>13142</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2119</t>
+          <t>2123</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14758</t>
+          <t>14899</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5106</t>
+          <t>5723</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21997</t>
+          <t>22285</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>408452</t>
+          <t>409211</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>420751</t>
+          <t>420877</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>496746</t>
+          <t>496605</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>509385</t>
+          <t>509381</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>911860</t>
+          <t>911572</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>928751</t>
+          <t>928134</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,39%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4922</t>
+          <t>5202</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19311</t>
+          <t>19786</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1759</t>
+          <t>1860</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9513</t>
+          <t>9214</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8637</t>
+          <t>8288</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25864</t>
+          <t>24378</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>516863</t>
+          <t>516388</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>531252</t>
+          <t>530972</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>530710</t>
+          <t>531009</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>538464</t>
+          <t>538363</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1050532</t>
+          <t>1052018</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1067759</t>
+          <t>1068108</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,23%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>535</t>
+          <t>578</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9250</t>
+          <t>9151</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2762</t>
+          <t>2725</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10633</t>
+          <t>10138</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4164</t>
+          <t>4695</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16050</t>
+          <t>15687</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>872984</t>
+          <t>873083</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>881699</t>
+          <t>881656</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,94%</t>
+          <t>99,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>700904</t>
+          <t>701399</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>708775</t>
+          <t>708812</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1577721</t>
+          <t>1578084</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1589607</t>
+          <t>1589076</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,71%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2647</t>
+          <t>2727</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12816</t>
+          <t>13279</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5428</t>
+          <t>4328</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4061</t>
+          <t>4302</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14500</t>
+          <t>15321</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>546430</t>
+          <t>545967</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>556599</t>
+          <t>556519</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>540556</t>
+          <t>541656</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1090731</t>
+          <t>1089910</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1101170</t>
+          <t>1100929</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,61%</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5654</t>
+          <t>3610</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4347</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6042</t>
+          <t>5883</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,6%</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>361891</t>
+          <t>363935</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>603922</t>
+          <t>603442</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>969292</t>
+          <t>969451</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>974878</t>
+          <t>975334</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,95%</t>
+          <t>100,0%</t>
         </is>
       </c>
     </row>
@@ -2788,97 +2788,97 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>377</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>1183</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>1731</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>377</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>1897</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>2162</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,05%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>377</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>1907</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,05%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,31%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>281576</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>423376</t>
+          <t>423542</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>706125</t>
+          <t>705870</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>23831</t>
+          <t>23553</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>57128</t>
+          <t>57918</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>15475</t>
+          <t>15300</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>35432</t>
+          <t>36286</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>44527</t>
+          <t>44134</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>82700</t>
+          <t>81536</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3393171</t>
+          <t>3392381</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3426468</t>
+          <t>3426746</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3620078</t>
+          <t>3619224</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3640035</t>
+          <t>3640210</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>7023108</t>
+          <t>7024272</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7061281</t>
+          <t>7061674</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P25D_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P25D_R-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>10458</t>
+          <t>13326</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2876</t>
+          <t>4632</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27584</t>
+          <t>31607</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4020</t>
+          <t>3966</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13279</t>
+          <t>15263</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>14478</t>
+          <t>17292</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5743</t>
+          <t>7212</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32241</t>
+          <t>34405</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>389529</t>
+          <t>394467</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>372403</t>
+          <t>376186</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>397111</t>
+          <t>403161</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,27 +873,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>309180</t>
+          <t>358546</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>299921</t>
+          <t>347249</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>698709</t>
+          <t>753013</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>680946</t>
+          <t>735900</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>707444</t>
+          <t>763093</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5527</t>
+          <t>5808</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>1598</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13142</t>
+          <t>15279</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>6626</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2123</t>
+          <t>2477</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14899</t>
+          <t>15312</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>11716</t>
+          <t>12434</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5723</t>
+          <t>6214</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22285</t>
+          <t>22926</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>416826</t>
+          <t>469801</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>409211</t>
+          <t>460330</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>420877</t>
+          <t>474011</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>505315</t>
+          <t>494457</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>496605</t>
+          <t>485771</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>509381</t>
+          <t>498606</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>922141</t>
+          <t>964258</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>911572</t>
+          <t>953766</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>928134</t>
+          <t>970478</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,36%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>422353</t>
+          <t>475609</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>422353</t>
+          <t>475609</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>422353</t>
+          <t>475609</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>933857</t>
+          <t>976692</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>933857</t>
+          <t>976692</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>933857</t>
+          <t>976692</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,22 +1411,22 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>10707</t>
+          <t>12124</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5202</t>
+          <t>6039</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19786</t>
+          <t>22290</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4382</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>2259</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9214</t>
+          <t>10032</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>15088</t>
+          <t>17408</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8288</t>
+          <t>9957</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24378</t>
+          <t>27169</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -1524,27 +1524,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>525467</t>
+          <t>607535</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>516388</t>
+          <t>597369</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>530972</t>
+          <t>613620</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>535841</t>
+          <t>614503</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>531009</t>
+          <t>609755</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>538363</t>
+          <t>617528</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,17 +1594,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1061308</t>
+          <t>1222037</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1052018</t>
+          <t>1212276</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1068108</t>
+          <t>1229488</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,2%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536174</t>
+          <t>619659</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536174</t>
+          <t>619659</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536174</t>
+          <t>619659</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>540223</t>
+          <t>619787</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>540223</t>
+          <t>619787</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>540223</t>
+          <t>619787</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1076396</t>
+          <t>1239445</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1076396</t>
+          <t>1239445</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1076396</t>
+          <t>1239445</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3230</t>
+          <t>3488</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>1128</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9151</t>
+          <t>9347</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5965</t>
+          <t>6627</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2725</t>
+          <t>3476</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10138</t>
+          <t>12011</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>9195</t>
+          <t>10115</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4695</t>
+          <t>4991</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15687</t>
+          <t>16348</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>879004</t>
+          <t>691474</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>873083</t>
+          <t>685615</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>881656</t>
+          <t>693834</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,93%</t>
+          <t>99,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>705572</t>
+          <t>728851</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>701399</t>
+          <t>723467</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>708812</t>
+          <t>732002</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1584576</t>
+          <t>1420326</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1578084</t>
+          <t>1414093</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1589076</t>
+          <t>1425450</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,65%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>882234</t>
+          <t>694962</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>882234</t>
+          <t>694962</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>882234</t>
+          <t>694962</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>711537</t>
+          <t>735478</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>711537</t>
+          <t>735478</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>711537</t>
+          <t>735478</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1593771</t>
+          <t>1430441</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1593771</t>
+          <t>1430441</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1593771</t>
+          <t>1430441</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>6626</t>
+          <t>6806</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2727</t>
+          <t>2776</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13279</t>
+          <t>12931</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1661</t>
+          <t>1766</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>476</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4328</t>
+          <t>4959</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>8287</t>
+          <t>8571</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4302</t>
+          <t>4007</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15321</t>
+          <t>15193</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>552620</t>
+          <t>600523</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>545967</t>
+          <t>594398</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>556519</t>
+          <t>604553</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,27 +2245,27 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>544323</t>
+          <t>605028</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>541656</t>
+          <t>601835</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>545542</t>
+          <t>606318</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1096944</t>
+          <t>1205552</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1089910</t>
+          <t>1198930</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1100929</t>
+          <t>1210116</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,67%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>559246</t>
+          <t>607329</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>559246</t>
+          <t>607329</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>559246</t>
+          <t>607329</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>545984</t>
+          <t>606794</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>545984</t>
+          <t>606794</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>545984</t>
+          <t>606794</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1105231</t>
+          <t>1214123</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1105231</t>
+          <t>1214123</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1105231</t>
+          <t>1214123</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3610</t>
+          <t>5272</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1146</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4347</t>
+          <t>4537</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2338</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>623</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5883</t>
+          <t>7342</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -2553,27 +2553,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>366681</t>
+          <t>405359</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>363935</t>
+          <t>401140</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>367545</t>
+          <t>406412</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2588,27 +2588,27 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>606643</t>
+          <t>437193</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>603442</t>
+          <t>433941</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>607789</t>
+          <t>438478</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>973324</t>
+          <t>842552</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>969451</t>
+          <t>837548</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>975334</t>
+          <t>844267</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,93%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>367545</t>
+          <t>406412</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>367545</t>
+          <t>406412</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>367545</t>
+          <t>406412</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>607789</t>
+          <t>438478</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>607789</t>
+          <t>438478</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>607789</t>
+          <t>438478</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>975334</t>
+          <t>844890</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>975334</t>
+          <t>844890</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>975334</t>
+          <t>844890</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>390</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1731</t>
+          <t>2341</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>390</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2162</t>
+          <t>1969</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,25%</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2931,27 +2931,27 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>424896</t>
+          <t>463547</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>423542</t>
+          <t>461596</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>425273</t>
+          <t>463937</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>99,92%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2966,17 +2966,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>707655</t>
+          <t>773746</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>705870</t>
+          <t>772167</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>708032</t>
+          <t>774136</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425273</t>
+          <t>463937</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425273</t>
+          <t>463937</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425273</t>
+          <t>463937</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708032</t>
+          <t>774136</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708032</t>
+          <t>774136</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708032</t>
+          <t>774136</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>37411</t>
+          <t>42606</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>23553</t>
+          <t>28507</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>57918</t>
+          <t>62490</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>23740</t>
+          <t>25944</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>15300</t>
+          <t>17746</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>36286</t>
+          <t>39041</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>61151</t>
+          <t>68550</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>44134</t>
+          <t>50758</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>81536</t>
+          <t>92172</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3412888</t>
+          <t>3479357</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3392381</t>
+          <t>3459473</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3426746</t>
+          <t>3493456</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3631770</t>
+          <t>3702126</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3619224</t>
+          <t>3689029</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3640210</t>
+          <t>3710324</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>7044657</t>
+          <t>7181482</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>7024272</t>
+          <t>7157860</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7061674</t>
+          <t>7199274</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3450299</t>
+          <t>3521963</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3450299</t>
+          <t>3521963</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3450299</t>
+          <t>3521963</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3655510</t>
+          <t>3728070</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3655510</t>
+          <t>3728070</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3655510</t>
+          <t>3728070</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7105808</t>
+          <t>7250032</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7105808</t>
+          <t>7250032</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7105808</t>
+          <t>7250032</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
